--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="22283" activeTab="1"/>
+    <workbookView windowHeight="22283" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="量化一-收盘数据" sheetId="1" r:id="rId1"/>
@@ -221,7 +221,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +238,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
@@ -697,176 +704,182 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -875,9 +888,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1234,43 +1244,43 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" ht="39" customHeight="1" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="9"/>
     </row>
     <row r="4" ht="39" customHeight="1" spans="1:3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="11">
         <v>85001</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1281,10 +1291,10 @@
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="10" t="s">
@@ -1292,105 +1302,105 @@
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="5">
         <v>29878026.93</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="5">
         <v>88056.09</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="5">
         <v>5917159.83</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" ht="72" customHeight="1" spans="1:3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="10" t="s">
@@ -1398,17 +1408,17 @@
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
     </row>
     <row r="20" ht="72" customHeight="1" spans="1:3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="10" t="s">
@@ -1416,11 +1426,11 @@
       </c>
     </row>
     <row r="21" ht="55.5" customHeight="1" spans="1:3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1453,43 +1463,43 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" ht="39" customHeight="1" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="9"/>
     </row>
     <row r="4" ht="39" customHeight="1" spans="1:3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1500,10 +1510,10 @@
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="5">
         <v>10000000</v>
       </c>
       <c r="C6" s="10" t="s">
@@ -1511,127 +1521,127 @@
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="5">
         <v>33961287.1</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="5">
         <v>4000000</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="12">
         <v>-80842.3</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="5">
         <v>3919157.7</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="5">
         <v>4000000</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="12">
         <v>-38712.9</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="5">
         <v>3961287.1</v>
       </c>
-      <c r="C13" s="6"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="5">
         <v>88056.09</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="5">
         <v>10000000</v>
       </c>
-      <c r="C17" s="6"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
     </row>
     <row r="20" ht="72" customHeight="1" spans="1:3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="10" t="s">
@@ -1639,17 +1649,17 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
     </row>
     <row r="22" ht="72" customHeight="1" spans="1:3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="10" t="s">
@@ -1680,133 +1690,138 @@
   <sheetPr/>
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="17.9722222222222" customWidth="1"/>
+    <col min="2" max="2" width="49.787037037037" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="28.5" customHeight="1" spans="1:2">
+      <c r="A1" s="7" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="8"/>
+    </row>
+    <row r="2" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+    <row r="4" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="5">
         <v>85012</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+    <row r="6" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+    <row r="7" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+    <row r="8" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
+    <row r="9" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="5">
         <v>478342.45</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="5">
         <v>10028560.37</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
+    <row r="12" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="5">
         <v>4.7698</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
+    <row r="13" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" ht="88.5" customHeight="1" spans="1:2">
+      <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
+    <row r="15" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
+    <row r="17" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="1"/>
+      <c r="B17" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A13:B13"/>
@@ -1823,8 +1838,12 @@
   <sheetPr/>
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="17.9722222222222" customWidth="1"/>
+    <col min="2" max="2" width="49.787037037037" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" ht="39" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1832,123 +1851,123 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="B2" s="3"/>
+    </row>
+    <row r="3" ht="22.5" customHeight="1" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+    <row r="4" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="5">
         <v>85012</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+    <row r="6" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="5">
         <v>20000000</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+    <row r="7" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="5">
         <v>10000000</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+    <row r="8" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
+    <row r="9" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="5">
         <v>3000000</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="5">
         <v>20000000</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
+    <row r="12" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
+    <row r="13" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" ht="88.5" customHeight="1" spans="1:2">
+      <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
+    <row r="15" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
+    <row r="17" ht="22.5" customHeight="1" spans="1:2">
+      <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="1"/>
+      <c r="B17" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -221,6 +221,126 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6096000" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6096000" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6096000" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6096000" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -737,7 +857,7 @@
           <t>昨日单位净值</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="2" t="n">
         <v>0.9959</v>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -914,6 +1034,7 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1172,7 +1293,7 @@
           <t>昨日单位净值</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="2" t="n">
         <v>1.132</v>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -1347,6 +1468,7 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1430,7 +1552,7 @@
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>交易所回购</t>
+          <t>总盈利/亏损</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1442,7 +1564,7 @@
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>总盈利/亏损</t>
+          <t>收益率</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1505,7 +1627,7 @@
           <t>昨日单位净值</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="2" t="n">
         <v>1.0029</v>
       </c>
     </row>
@@ -1587,7 +1709,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>今日交易 27 只期货合约 成交金额 531.77 万元
+          <t>今日交易 35 只期货合约 成交金额 531.77 万元
 卖出开仓: 7 只
 买入平仓: 7 只
 买入开仓: 12 只
@@ -1612,7 +1734,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>共持仓 34只期货，其中空仓: 53 只,多仓: 98 只</t>
+          <t>共持仓 34只期货，其中空仓: 18 只,多仓: 16 只</t>
         </is>
       </c>
       <c r="C24" s="11" t="n"/>
@@ -1654,6 +1776,7 @@
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1737,7 +1860,7 @@
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>交易所回购</t>
+          <t>总盈利/亏损</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
@@ -1747,7 +1870,7 @@
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>总盈利/亏损</t>
+          <t>收益率</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1810,7 +1933,7 @@
           <t>昨日单位净值</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1892,7 +2015,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>今日交易 27 只期货合约 成交金额 531.77 万元
+          <t>今日交易 35 只期货合约 成交金额 531.77 万元
 卖出开仓: 7 只
 买入平仓: 7 只
 买入开仓: 12 只
@@ -1917,7 +2040,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>共持仓 34只期货，其中空仓: 53 只,多仓: 98 只</t>
+          <t>共持仓 34只期货，其中空仓: 18 只,多仓: 16 只</t>
         </is>
       </c>
       <c r="C24" s="11" t="n"/>
@@ -1959,5 +2082,6 @@
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -232,20 +232,20 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6096000" cy="4572000"/>
+    <ext cx="8572500" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -254,7 +254,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -262,20 +262,20 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6096000" cy="4572000"/>
+    <ext cx="8572500" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -284,7 +284,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -292,20 +292,20 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6096000" cy="4572000"/>
+    <ext cx="8572500" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -322,20 +322,20 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6096000" cy="4572000"/>
+    <ext cx="8572500" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>85001.0</t>
+          <t>85001</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>

--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -232,20 +232,20 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="5715000"/>
+    <ext cx="9525000" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -254,7 +254,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -262,20 +262,20 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="5715000"/>
+    <ext cx="9525000" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -284,7 +284,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -292,20 +292,20 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="5715000"/>
+    <ext cx="9525000" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -314,7 +314,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -322,20 +322,20 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="5715000"/>
+    <ext cx="9525000" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.9959</v>
+        <v>1.012</v>
       </c>
       <c r="C18" s="5" t="n"/>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>0.0034%</t>
+          <t>-1.5865%</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.132</v>
+        <v>1.012</v>
       </c>
       <c r="C20" s="5" t="n"/>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>0.0038%</t>
+          <t>11.8632%</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.0029</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>-0.0044%</t>
+          <t>-0.9025%</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>97.6306%</t>
         </is>
       </c>
     </row>

--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1.012</v>
+        <v>0.8003</v>
       </c>
       <c r="C18" s="5" t="n"/>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>-1.5865%</t>
+          <t>24.4451%</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.012</v>
+        <v>0.8006</v>
       </c>
       <c r="C20" s="5" t="n"/>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>11.8632%</t>
+          <t>41.3993%</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.012</v>
+        <v>0.8445</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>-0.9025%</t>
+          <t>18.7515%</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.012</v>
+        <v>0.8245</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>97.6306%</t>
+          <t>142.5713%</t>
         </is>
       </c>
     </row>

--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -9,8 +9,6 @@
   <sheets>
     <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="量化二-收盘数据" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="量化二-结算数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -116,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -143,9 +141,6 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -254,66 +249,6 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525000" cy="5715000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525000" cy="5715000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1470,618 +1405,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>统计日期</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>2025-04-10, （金额单位：元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="27" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>一、账户资产及收益情况</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>账户名称</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>量化二</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>账户编号</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>85012</v>
-      </c>
-    </row>
-    <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>资产单元名称</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>量化二-投机单元</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>账户资产净值</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>10028560.37</v>
-      </c>
-    </row>
-    <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>总盈利/亏损</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>27477.04</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>收益率</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>0.2748%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>二、净值列示</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>资产净值</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>10028560.37</v>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>总份额</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>期初单位净值</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>昨日单位净值</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0.8445</v>
-      </c>
-    </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1.0029</v>
-      </c>
-    </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>日净值增长率</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>18.7515%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>三、保证金使用情况</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>占用</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>478342.45</v>
-      </c>
-    </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>账户权益</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>10028560.37</v>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>风险度</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>4.7698%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>四、交易情况</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="140" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>交易方向及数量</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>今日交易 35 只期货合约 成交金额 531.77 万元
-卖出开仓: 7 只
-买入平仓: 7 只
-买入开仓: 12 只
-卖出平仓: 9 只</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>五、持仓情况</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="140" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>持仓品种及数量</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>共持仓 34只期货，其中空仓: 18 只,多仓: 16 只</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>注：交易情况中的商品期货数量未去重。</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="B15"/>
-    <mergeCell ref="B6"/>
-    <mergeCell ref="B24"/>
-    <mergeCell ref="B20"/>
-    <mergeCell ref="B5"/>
-    <mergeCell ref="B4"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="B7"/>
-    <mergeCell ref="B16"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B12"/>
-    <mergeCell ref="B18"/>
-    <mergeCell ref="B11"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="B14"/>
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B8"/>
-    <mergeCell ref="B13"/>
-    <mergeCell ref="B10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="B19"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>统计日期</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-10, （金额单位：元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="27" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>一、账户资产及收益情况</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>账户名称</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>量化二</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>账户编号</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>85012</v>
-      </c>
-    </row>
-    <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>资产单元名称</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>量化二-投机单元</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>账户资产净值</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>总盈利/亏损</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>收益率</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>二、净值列示</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>实收资本</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>资产净值</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>总份额</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>期初单位净值</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>昨日单位净值</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0.8245</v>
-      </c>
-    </row>
-    <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>日净值增长率</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>142.5713%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>三、保证金使用情况</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>占用</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>账户权益</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>风险度</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="27" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>四、交易情况</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="140" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>交易方向及数量</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>今日交易 35 只期货合约 成交金额 531.77 万元
-卖出开仓: 7 只
-买入平仓: 7 只
-买入开仓: 12 只
-卖出平仓: 9 只</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>五、持仓情况</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="140" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>持仓品种及数量</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>共持仓 34只期货，其中空仓: 18 只,多仓: 16 只</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>注：交易情况中的商品期货数量未去重。</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="B15"/>
-    <mergeCell ref="B6"/>
-    <mergeCell ref="B24"/>
-    <mergeCell ref="B20"/>
-    <mergeCell ref="B5"/>
-    <mergeCell ref="B4"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="B7"/>
-    <mergeCell ref="B16"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="B22"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="B12"/>
-    <mergeCell ref="B18"/>
-    <mergeCell ref="B11"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="B14"/>
-    <mergeCell ref="B1"/>
-    <mergeCell ref="B8"/>
-    <mergeCell ref="B13"/>
-    <mergeCell ref="B10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="B19"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="量化一-收盘数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="量化一-结算数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="量化一-结算数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="量化一-收盘数据" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,6 +132,9 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -793,7 +796,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.8003</v>
+        <v>0.99593</v>
       </c>
       <c r="C18" s="5" t="n"/>
     </row>
@@ -804,7 +807,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.9959</v>
+        <v>0.99593</v>
       </c>
       <c r="C19" s="5" t="n"/>
     </row>
@@ -816,7 +819,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>24.4451%</t>
+          <t>0.00042%</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -892,18 +895,8 @@
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>今日交易: 0 只股指期货合约, 1 只股指期权合约， 成交金额 2.78 万元
-买入平仓: HO2506-P-2550(2 手),
-卖出平仓: HO2506-P-2550(2 手)</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>买入股票: 0 只, 卖出股票: 0 只, 股票合计成交金额: 0.0 万元</t>
-        </is>
-      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -920,21 +913,21 @@
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>当前持有: 0 只股指期货合约, 3 只股指期权合约
 权利仓: HO2506-P-2550(2 手),
 义务仓: MO2504-C-6400(1 手),HO2506-P-2550(2 手)</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>股票: 0 只</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">注:
 1、总盈利/亏损(不含逆回购): 根据032盈亏数据计算,未扣除中金所申报费。
@@ -1229,7 +1222,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.8006</v>
+        <v>1.13204</v>
       </c>
       <c r="C20" s="5" t="n"/>
     </row>
@@ -1240,7 +1233,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.132</v>
+        <v>1.13204</v>
       </c>
       <c r="C21" s="5" t="n"/>
     </row>
@@ -1252,7 +1245,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>41.3993%</t>
+          <t>0.00026%</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -1272,7 +1265,7 @@
           <t>占用</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="11" t="n">
         <v>88056.09</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1328,18 +1321,8 @@
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>今日交易: 0 只股指期货合约, 1 只股指期权合约， 成交金额 2.78 万元
-买入平仓: HO2506-P-2550(2 手),
-卖出平仓: HO2506-P-2550(2 手)</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>买入股票: 0 只, 卖出股票: 0 只, 股票合计成交金额: 0.0 万元</t>
-        </is>
-      </c>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -1356,21 +1339,21 @@
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>当前持有: 0 只股指期货合约, 3 只股指期权合约
 权利仓: HO2506-P-2550(2 手),
 义务仓: MO2504-C-6400(1 手),HO2506-P-2550(2 手)</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>股票: 0 只</t>
         </is>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>注:
 1、盈利/亏损（不含逆回购）数据暂未包含中金所申报费，盈利/亏损（含逆回购）数据已包含中金所申报费。</t>

--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="量化一-结算数据" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="量化一-收盘数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="量化二-结算数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="量化二-收盘数据" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -114,12 +116,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -130,16 +129,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -252,6 +251,66 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -584,7 +643,7 @@
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
@@ -596,57 +655,57 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>一、账户资产及收益情况</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="5" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="4" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>账户名称</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>量化一</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
+      <c r="C3" s="4" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>账户编号</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="6" t="n">
         <v>85001</v>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="4" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>资产单元名称</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>量化一-投机单元</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>权益类一单元</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>单元资产净值</t>
         </is>
@@ -659,7 +718,7 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>账户资产净值</t>
         </is>
@@ -667,10 +726,10 @@
       <c r="B7" s="7" t="n">
         <v>29878026.93</v>
       </c>
-      <c r="C7" s="5" t="n"/>
+      <c r="C7" s="4" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>交易所回购</t>
         </is>
@@ -685,7 +744,7 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>总盈利/亏损（不含逆回购）</t>
         </is>
@@ -695,23 +754,23 @@
           <t>-164014.47</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n"/>
+      <c r="C9" s="4" t="n"/>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>收益率（不含逆回购）</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>-0.5467%</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="4" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>总盈利/亏损（含逆回购）</t>
         </is>
@@ -721,10 +780,10 @@
           <t>-121973.07</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n"/>
+      <c r="C11" s="4" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>收益率（含逆回购）</t>
         </is>
@@ -734,19 +793,19 @@
           <t>-0.4066%</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="4" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="4" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>实收资本</t>
         </is>
@@ -754,10 +813,10 @@
       <c r="B14" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="4" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>资产净值</t>
         </is>
@@ -765,10 +824,10 @@
       <c r="B15" s="7" t="n">
         <v>29878026.93</v>
       </c>
-      <c r="C15" s="5" t="n"/>
+      <c r="C15" s="4" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>总份额</t>
         </is>
@@ -776,10 +835,10 @@
       <c r="B16" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="4" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>期初单位净值</t>
         </is>
@@ -787,54 +846,54 @@
       <c r="B17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="5" t="n"/>
+      <c r="C17" s="4" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>昨日单位净值</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="6" t="n">
+        <v>0.8003</v>
+      </c>
+      <c r="C18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>单位净值</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
         <v>0.99593</v>
       </c>
-      <c r="C18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0.99593</v>
-      </c>
-      <c r="C19" s="5" t="n"/>
+      <c r="C19" s="4" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>日净值增长率</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>0.00042%</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>24.44511%</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="5" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="4" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>占用</t>
         </is>
@@ -842,14 +901,14 @@
       <c r="B22" s="7" t="n">
         <v>88056.09</v>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>账户权益</t>
         </is>
@@ -857,14 +916,14 @@
       <c r="B23" s="7" t="n">
         <v>5917159.83</v>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>风险度</t>
         </is>
@@ -874,60 +933,70 @@
           <t>1.488%</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="5" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="4" t="n"/>
     </row>
     <row r="26" ht="140" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>今日交易: 0 只股指期货合约, 1 只股指期权合约， 成交金额 2.78 万元
+买入平仓: HO2506-P-2550(2 手),
+卖出平仓: HO2506-P-2550(2 手)</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>买入股票: 0 只, 卖出股票: 0 只, 股票合计成交金额: 0.0 万元</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="5" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="4" t="n"/>
     </row>
     <row r="28" ht="140" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>当前持有: 0 只股指期货合约, 3 只股指期权合约
 权利仓: HO2506-P-2550(2 手),
 义务仓: MO2504-C-6400(1 手),HO2506-P-2550(2 手)</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>股票: 0 只</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">注:
 1、总盈利/亏损(不含逆回购): 根据032盈亏数据计算,未扣除中金所申报费。
@@ -935,8 +1004,6 @@
 </t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -986,7 +1053,7 @@
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
@@ -998,59 +1065,59 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>一、账户资产及收益情况</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="5" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="4" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>账户名称</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>量化一</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
+      <c r="C3" s="4" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>账户编号</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>85001</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="4" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>资产单元名称</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>量化一-投机单元</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>权益类一单元</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>单元资产净值</t>
         </is>
@@ -1063,7 +1130,7 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>账户资产净值</t>
         </is>
@@ -1071,10 +1138,10 @@
       <c r="B7" s="7" t="n">
         <v>33961287.1</v>
       </c>
-      <c r="C7" s="5" t="n"/>
+      <c r="C7" s="4" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>交易所回购</t>
         </is>
@@ -1089,7 +1156,7 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>盈利/亏损（不含逆回购）</t>
         </is>
@@ -1102,7 +1169,7 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>总盈利/亏损（不含逆回购）</t>
         </is>
@@ -1110,10 +1177,10 @@
       <c r="B10" s="7" t="n">
         <v>3919157.7</v>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="4" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>收益率（不含逆回购）</t>
         </is>
@@ -1123,10 +1190,10 @@
           <t>13.0639%</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n"/>
+      <c r="C11" s="4" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>盈利/亏损（含逆回购）</t>
         </is>
@@ -1139,7 +1206,7 @@
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>总盈利/亏损（含逆回购）</t>
         </is>
@@ -1147,10 +1214,10 @@
       <c r="B13" s="7" t="n">
         <v>3961287.100000001</v>
       </c>
-      <c r="C13" s="5" t="n"/>
+      <c r="C13" s="4" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>收益率（含逆回购）</t>
         </is>
@@ -1160,19 +1227,19 @@
           <t>13.2043%</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="4" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="4" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>实收资本</t>
         </is>
@@ -1180,10 +1247,10 @@
       <c r="B16" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="4" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>资产净值</t>
         </is>
@@ -1191,10 +1258,10 @@
       <c r="B17" s="7" t="n">
         <v>33961287.1</v>
       </c>
-      <c r="C17" s="5" t="n"/>
+      <c r="C17" s="4" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>总份额</t>
         </is>
@@ -1202,10 +1269,10 @@
       <c r="B18" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="4" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>期初单位净值</t>
         </is>
@@ -1213,69 +1280,69 @@
       <c r="B19" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="5" t="n"/>
+      <c r="C19" s="4" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>昨日单位净值</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="6" t="n">
+        <v>0.8006</v>
+      </c>
+      <c r="C20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>单位净值</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
         <v>1.13204</v>
       </c>
-      <c r="C20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>单位净值</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>1.13204</v>
-      </c>
-      <c r="C21" s="5" t="n"/>
+      <c r="C21" s="4" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>日净值增长率</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>0.00026%</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>41.39931%</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="5" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="4" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>占用</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="10" t="n">
         <v>88056.09</v>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>账户权益</t>
         </is>
@@ -1283,14 +1350,14 @@
       <c r="B25" s="7" t="n">
         <v>10000000</v>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>风险度</t>
         </is>
@@ -1300,67 +1367,75 @@
           <t>0.8806%</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="5" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="4" t="n"/>
     </row>
     <row r="28" ht="140" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>交易方向及数量</t>
         </is>
       </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>今日交易: 0 只股指期货合约, 1 只股指期权合约， 成交金额 2.78 万元
+买入平仓: HO2506-P-2550(2 手),
+卖出平仓: HO2506-P-2550(2 手)</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>买入股票: 0 只, 卖出股票: 0 只, 股票合计成交金额: 0.0 万元</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="5" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="4" t="n"/>
     </row>
     <row r="30" ht="140" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>持仓品种及数量</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>当前持有: 0 只股指期货合约, 3 只股指期权合约
 权利仓: HO2506-P-2550(2 手),
 义务仓: MO2504-C-6400(1 手),HO2506-P-2550(2 手)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>股票: 0 只</t>
         </is>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>注:
 1、盈利/亏损（不含逆回购）数据暂未包含中金所申报费，盈利/亏损（含逆回购）数据已包含中金所申报费。</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1388,4 +1463,616 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>统计日期</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>2025-04-10, （金额单位：元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一、账户资产及收益情况</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>账户名称</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>量化二</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>账户编号</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>85012</v>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>资产单元名称</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>量化二-投机单元</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>账户资产净值</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>10028560.37</v>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>总盈利/亏损</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>27477.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>收益率</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>0.2748%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>二、净值列示</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>资产净值</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>10028560.37</v>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>昨日单位净值</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0.8445</v>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>单位净值</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1.00286</v>
+      </c>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>日净值增长率</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>18.75145%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>三、保证金使用情况</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>占用</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>478342.45</v>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>10028560.37</v>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>风险度</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>4.7698%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>四、交易情况</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="140" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>交易方向及数量</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>今日交易 35 只期货合约 成交金额 531.77 万元
+卖出开仓: 7 只
+买入平仓: 7 只
+买入开仓: 12 只
+卖出平仓: 9 只</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>五、持仓情况</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="140" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>持仓品种及数量</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>共持仓 34只期货，其中空仓: 18 只,多仓: 16 只</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>注：交易情况中的商品期货数量未去重。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B6"/>
+    <mergeCell ref="B24"/>
+    <mergeCell ref="B20"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="B4"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="B3"/>
+    <mergeCell ref="B22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B12"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="B1"/>
+    <mergeCell ref="B8"/>
+    <mergeCell ref="B13"/>
+    <mergeCell ref="B10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>统计日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-10, （金额单位：元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>一、账户资产及收益情况</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>账户名称</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>量化二</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>账户编号</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>85012</v>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>资产单元名称</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>量化二-投机单元</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>账户资产净值</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="7" ht="27" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>总盈利/亏损</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="8" ht="27" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>收益率</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>二、净值列示</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>资产净值</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="12" ht="27" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>总份额</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>昨日单位净值</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0.8245</v>
+      </c>
+    </row>
+    <row r="15" ht="27" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>单位净值</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" ht="27" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>日净值增长率</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>142.57126%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>三、保证金使用情况</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>占用</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="19" ht="27" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>账户权益</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="20" ht="27" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>风险度</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>四、交易情况</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="140" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>交易方向及数量</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>今日交易 35 只期货合约 成交金额 531.77 万元
+卖出开仓: 7 只
+买入平仓: 7 只
+买入开仓: 12 只
+卖出平仓: 9 只</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>五、持仓情况</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="140" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>持仓品种及数量</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>共持仓 34只期货，其中空仓: 18 只,多仓: 16 只</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>注：交易情况中的商品期货数量未去重。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B6"/>
+    <mergeCell ref="B24"/>
+    <mergeCell ref="B20"/>
+    <mergeCell ref="B5"/>
+    <mergeCell ref="B4"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="B3"/>
+    <mergeCell ref="B22"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B12"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="B1"/>
+    <mergeCell ref="B8"/>
+    <mergeCell ref="B13"/>
+    <mergeCell ref="B10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.8003</v>
+        <v>1.13204</v>
       </c>
       <c r="C18" s="4" t="n"/>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>24.44511%</t>
+          <t>-12.02305%</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.8006</v>
+        <v>0.99593</v>
       </c>
       <c r="C20" s="4" t="n"/>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>41.39931%</t>
+          <t>13.66691%</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1548,10 +1548,8 @@
           <t>总盈利/亏损</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>27477.04</t>
-        </is>
+      <c r="B7" s="7" t="n">
+        <v>28560.37</v>
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
@@ -1621,7 +1619,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.8445</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1642,7 +1640,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>18.75145%</t>
+          <t>-49.8572%</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1924,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.8245</v>
+        <v>1.00286</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1947,7 +1945,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>142.57126%</t>
+          <t>99.42963%</t>
         </is>
       </c>
     </row>

--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1.13204</v>
+        <v>0.8006</v>
       </c>
       <c r="C18" s="4" t="n"/>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>-12.02305%</t>
+          <t>24.39848%</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.99593</v>
+        <v>0.8003</v>
       </c>
       <c r="C20" s="4" t="n"/>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>13.66691%</t>
+          <t>41.45232%</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>2</v>
+        <v>0.8245</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>-49.8572%</t>
+          <t>21.63202%</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1.00286</v>
+        <v>0.8445</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>99.42963%</t>
+          <t>136.82652%</t>
         </is>
       </c>
     </row>

--- a/test/4.10/量化业务日报-2025-04-10.xlsx
+++ b/test/4.10/量化业务日报-2025-04-10.xlsx
@@ -218,126 +218,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525000" cy="5715000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525000" cy="5715000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525000" cy="5715000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525000" cy="5715000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -855,7 +735,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>0.8006</v>
+        <v>0.99593</v>
       </c>
       <c r="C18" s="4" t="n"/>
     </row>
@@ -878,7 +758,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>24.39848%</t>
+          <t>0.00042%</t>
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
@@ -1029,7 +909,6 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1289,7 +1168,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0.8003</v>
+        <v>1.13204</v>
       </c>
       <c r="C20" s="4" t="n"/>
     </row>
@@ -1312,7 +1191,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>41.45232%</t>
+          <t>0.00026%</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1461,7 +1340,6 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1619,7 +1497,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.8245</v>
+        <v>1.00286</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1640,7 +1518,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>21.63202%</t>
+          <t>-0.0004%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1644,6 @@
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1924,7 +1801,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.8445</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="27" customHeight="1">
@@ -1945,7 +1822,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>136.82652%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -2071,6 +1948,5 @@
     <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>